--- a/data/durf-roadmap.xlsx
+++ b/data/durf-roadmap.xlsx
@@ -96,17 +96,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2CA055"/>
+        <fgColor rgb="FF17A95D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B2882"/>
+        <fgColor rgb="FF5C1B61"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7303A"/>
+        <fgColor rgb="FF83201B"/>
       </patternFill>
     </fill>
   </fills>
@@ -917,7 +917,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>#2CA055</t>
+          <t>#17A95D</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>#7B2882</t>
+          <t>#5C1B61</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>#E7303A</t>
+          <t>#83201B</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1836,7 +1836,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G22" s="14" t="inlineStr"/>
       <c r="H22" s="7" t="inlineStr">
@@ -1849,11 +1849,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Slide timeline bar suggested months 3–18; the written months (12–48) are used here. Confirm with the theme lead.</t>
-        </is>
-      </c>
+      <c r="J22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="46" customHeight="1">
       <c r="A23" s="14" t="n">
@@ -1887,11 +1883,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Slide timeline bar suggested months 1–6; the written months (12–18) are used here. Confirm with the theme lead.</t>
-        </is>
-      </c>
+      <c r="J23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="46" customHeight="1">
       <c r="A24" s="14" t="n">
@@ -1988,7 +1980,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="G26" s="14" t="inlineStr"/>
       <c r="H26" s="7" t="inlineStr">
@@ -2001,11 +1993,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Slide timeline column also noted months 1–18; the written months (12–48) are used here. Confirm with the theme lead.</t>
-        </is>
-      </c>
+      <c r="J26" s="7" t="inlineStr"/>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="14" t="n">
@@ -2832,12 +2820,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Calendar month that project month 1 maps to. Format YYYY-MM.</t>
+          <t>Calendar month that project month 1 maps to. Format YYYY-MM. Project years and the month axis are counted from here.</t>
         </is>
       </c>
     </row>
